--- a/Operacional/clientes/hora-z/outputs/09-2026/Arquivos/15-inteligencia-dados-estoque-giro-margem_snapshot-2026-09-15.xlsx
+++ b/Operacional/clientes/hora-z/outputs/09-2026/Arquivos/15-inteligencia-dados-estoque-giro-margem_snapshot-2026-09-15.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Estoque parado" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Risco de ruptura" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Auditoria outliers cadastro" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sensibilidade custo fornecedor" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -553,7 +554,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,7 +594,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,7 +634,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,7 +674,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,7 +714,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,7 +754,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,7 +794,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,7 +834,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,7 +874,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,7 +914,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,7 +954,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,7 +994,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,7 +1034,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,7 +1074,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,7 +1114,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1168,7 +1154,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,7 +1194,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1255,7 +1239,6 @@
       <c r="K21" t="n">
         <v>10.99</v>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1301,7 +1284,6 @@
       <c r="K22" t="n">
         <v>33.04</v>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1347,7 +1329,6 @@
       <c r="K23" t="n">
         <v>31.43</v>
       </c>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1393,7 +1374,6 @@
       <c r="K24" t="n">
         <v>141.47</v>
       </c>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1439,7 +1419,6 @@
       <c r="K25" t="n">
         <v>155</v>
       </c>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1485,7 +1464,6 @@
       <c r="K26" t="n">
         <v>13.91</v>
       </c>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1531,7 +1509,6 @@
       <c r="K27" t="n">
         <v>32.39</v>
       </c>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1577,7 +1554,6 @@
       <c r="K28" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1623,7 +1599,6 @@
       <c r="K29" t="n">
         <v>157.16</v>
       </c>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1669,7 +1644,6 @@
       <c r="K30" t="n">
         <v>19.95</v>
       </c>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1715,7 +1689,6 @@
       <c r="K31" t="n">
         <v>157.18</v>
       </c>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1761,7 +1734,6 @@
       <c r="K32" t="n">
         <v>49.44</v>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1807,7 +1779,6 @@
       <c r="K33" t="n">
         <v>11.25</v>
       </c>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1853,7 +1824,6 @@
       <c r="K34" t="n">
         <v>148.76</v>
       </c>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1899,7 +1869,6 @@
       <c r="K35" t="n">
         <v>1.43</v>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1945,7 +1914,6 @@
       <c r="K36" t="n">
         <v>62.02</v>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1991,7 +1959,6 @@
       <c r="K37" t="n">
         <v>57.96</v>
       </c>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2037,7 +2004,6 @@
       <c r="K38" t="n">
         <v>17.41</v>
       </c>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2083,7 +2049,6 @@
       <c r="K39" t="n">
         <v>19.89</v>
       </c>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2129,7 +2094,6 @@
       <c r="K40" t="n">
         <v>33.79</v>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2175,7 +2139,6 @@
       <c r="K41" t="n">
         <v>73.80000000000001</v>
       </c>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2221,7 +2184,6 @@
       <c r="K42" t="n">
         <v>12.88</v>
       </c>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2267,7 +2229,6 @@
       <c r="K43" t="n">
         <v>3.35</v>
       </c>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2313,7 +2274,6 @@
       <c r="K44" t="n">
         <v>53.5</v>
       </c>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2359,7 +2319,6 @@
       <c r="K45" t="n">
         <v>26.82</v>
       </c>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2405,7 +2364,6 @@
       <c r="K46" t="n">
         <v>12.55</v>
       </c>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2451,7 +2409,6 @@
       <c r="K47" t="n">
         <v>29.75</v>
       </c>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2497,7 +2454,6 @@
       <c r="K48" t="n">
         <v>241.33</v>
       </c>
-      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2543,7 +2499,6 @@
       <c r="K49" t="n">
         <v>27.37</v>
       </c>
-      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2589,7 +2544,6 @@
       <c r="K50" t="n">
         <v>50.27</v>
       </c>
-      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2685,7 +2639,6 @@
       <c r="K52" t="n">
         <v>37.42</v>
       </c>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2731,7 +2684,6 @@
       <c r="K53" t="n">
         <v>71.64</v>
       </c>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2777,7 +2729,6 @@
       <c r="K54" t="n">
         <v>39.770001</v>
       </c>
-      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2823,7 +2774,6 @@
       <c r="K55" t="n">
         <v>193.0425</v>
       </c>
-      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2869,7 +2819,6 @@
       <c r="K56" t="n">
         <v>22.340001</v>
       </c>
-      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2915,7 +2864,6 @@
       <c r="K57" t="n">
         <v>108.95</v>
       </c>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2961,7 +2909,6 @@
       <c r="K58" t="n">
         <v>130.74</v>
       </c>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3057,7 +3004,6 @@
       <c r="K60" t="n">
         <v>32.170831</v>
       </c>
-      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3103,7 +3049,6 @@
       <c r="K61" t="n">
         <v>18.041665</v>
       </c>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3149,7 +3094,6 @@
       <c r="K62" t="n">
         <v>317.866665</v>
       </c>
-      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3195,7 +3139,6 @@
       <c r="K63" t="n">
         <v>399.96</v>
       </c>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3241,7 +3184,6 @@
       <c r="K64" t="n">
         <v>39.97</v>
       </c>
-      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3287,7 +3229,6 @@
       <c r="K65" t="n">
         <v>65.19</v>
       </c>
-      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3333,7 +3274,6 @@
       <c r="K66" t="n">
         <v>61.2</v>
       </c>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3379,7 +3319,6 @@
       <c r="K67" t="n">
         <v>37.8</v>
       </c>
-      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3425,7 +3364,6 @@
       <c r="K68" t="n">
         <v>39</v>
       </c>
-      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3471,7 +3409,6 @@
       <c r="K69" t="n">
         <v>39.6</v>
       </c>
-      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3517,7 +3454,6 @@
       <c r="K70" t="n">
         <v>12.908</v>
       </c>
-      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3563,7 +3499,6 @@
       <c r="K71" t="n">
         <v>29.31</v>
       </c>
-      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3609,7 +3544,6 @@
       <c r="K72" t="n">
         <v>4.96</v>
       </c>
-      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3655,7 +3589,6 @@
       <c r="K73" t="n">
         <v>15.44</v>
       </c>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3701,7 +3634,6 @@
       <c r="K74" t="n">
         <v>6.5</v>
       </c>
-      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3747,7 +3679,6 @@
       <c r="K75" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3793,7 +3724,6 @@
       <c r="K76" t="n">
         <v>40.8</v>
       </c>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3839,7 +3769,6 @@
       <c r="K77" t="n">
         <v>85.5</v>
       </c>
-      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3885,7 +3814,6 @@
       <c r="K78" t="n">
         <v>16.95</v>
       </c>
-      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3931,7 +3859,6 @@
       <c r="K79" t="n">
         <v>10.52</v>
       </c>
-      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3977,7 +3904,6 @@
       <c r="K80" t="n">
         <v>2.79</v>
       </c>
-      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4023,7 +3949,6 @@
       <c r="K81" t="n">
         <v>7.99</v>
       </c>
-      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4069,7 +3994,6 @@
       <c r="K82" t="n">
         <v>29.68</v>
       </c>
-      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4115,7 +4039,6 @@
       <c r="K83" t="n">
         <v>261.686667</v>
       </c>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4161,7 +4084,6 @@
       <c r="K84" t="n">
         <v>239.94</v>
       </c>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4207,7 +4129,6 @@
       <c r="K85" t="n">
         <v>23.01</v>
       </c>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4253,7 +4174,6 @@
       <c r="K86" t="n">
         <v>15.9</v>
       </c>
-      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4299,7 +4219,6 @@
       <c r="K87" t="n">
         <v>36.81</v>
       </c>
-      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4345,7 +4264,6 @@
       <c r="K88" t="n">
         <v>7.95</v>
       </c>
-      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4391,7 +4309,6 @@
       <c r="K89" t="n">
         <v>55.77</v>
       </c>
-      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4437,7 +4354,6 @@
       <c r="K90" t="n">
         <v>7.95</v>
       </c>
-      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4483,7 +4399,6 @@
       <c r="K91" t="n">
         <v>30.34</v>
       </c>
-      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4529,7 +4444,6 @@
       <c r="K92" t="n">
         <v>7.04</v>
       </c>
-      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4575,7 +4489,6 @@
       <c r="K93" t="n">
         <v>107.94</v>
       </c>
-      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4621,7 +4534,6 @@
       <c r="K94" t="n">
         <v>63.9</v>
       </c>
-      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4667,7 +4579,6 @@
       <c r="K95" t="n">
         <v>28.224</v>
       </c>
-      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4713,7 +4624,6 @@
       <c r="K96" t="n">
         <v>32.94</v>
       </c>
-      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4759,7 +4669,6 @@
       <c r="K97" t="n">
         <v>27.48</v>
       </c>
-      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4805,7 +4714,6 @@
       <c r="K98" t="n">
         <v>39.18</v>
       </c>
-      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4851,7 +4759,6 @@
       <c r="K99" t="n">
         <v>12.9311</v>
       </c>
-      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4897,7 +4804,6 @@
       <c r="K100" t="n">
         <v>7.25</v>
       </c>
-      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4943,7 +4849,6 @@
       <c r="K101" t="n">
         <v>18.52</v>
       </c>
-      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4989,7 +4894,6 @@
       <c r="K102" t="n">
         <v>55.6</v>
       </c>
-      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5035,7 +4939,6 @@
       <c r="K103" t="n">
         <v>123.41</v>
       </c>
-      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5081,7 +4984,6 @@
       <c r="K104" t="n">
         <v>44.64</v>
       </c>
-      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5177,7 +5079,6 @@
       <c r="K106" t="n">
         <v>27.31</v>
       </c>
-      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5223,7 +5124,6 @@
       <c r="K107" t="n">
         <v>9.43</v>
       </c>
-      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5269,7 +5169,6 @@
       <c r="K108" t="n">
         <v>9.99</v>
       </c>
-      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5315,7 +5214,6 @@
       <c r="K109" t="n">
         <v>21.5</v>
       </c>
-      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5361,7 +5259,6 @@
       <c r="K110" t="n">
         <v>11.8</v>
       </c>
-      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5407,7 +5304,6 @@
       <c r="K111" t="n">
         <v>13.9</v>
       </c>
-      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5453,7 +5349,6 @@
       <c r="K112" t="n">
         <v>47.3</v>
       </c>
-      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5499,7 +5394,6 @@
       <c r="K113" t="n">
         <v>11.36</v>
       </c>
-      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5545,7 +5439,6 @@
       <c r="K114" t="n">
         <v>14.8</v>
       </c>
-      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5591,7 +5484,6 @@
       <c r="K115" t="n">
         <v>4.79</v>
       </c>
-      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5637,7 +5529,6 @@
       <c r="K116" t="n">
         <v>7.6</v>
       </c>
-      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5683,7 +5574,6 @@
       <c r="K117" t="n">
         <v>20.95</v>
       </c>
-      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5729,7 +5619,6 @@
       <c r="K118" t="n">
         <v>2.58</v>
       </c>
-      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5775,7 +5664,6 @@
       <c r="K119" t="n">
         <v>44.85</v>
       </c>
-      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5821,7 +5709,6 @@
       <c r="K120" t="n">
         <v>29.85</v>
       </c>
-      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5867,7 +5754,6 @@
       <c r="K121" t="n">
         <v>16.39</v>
       </c>
-      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5913,7 +5799,6 @@
       <c r="K122" t="n">
         <v>37.5</v>
       </c>
-      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5959,7 +5844,6 @@
       <c r="K123" t="n">
         <v>182.4</v>
       </c>
-      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6005,7 +5889,6 @@
       <c r="K124" t="n">
         <v>386.1</v>
       </c>
-      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6051,7 +5934,6 @@
       <c r="K125" t="n">
         <v>58.185</v>
       </c>
-      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6097,7 +5979,6 @@
       <c r="K126" t="n">
         <v>41.03715</v>
       </c>
-      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6193,7 +6074,6 @@
       <c r="K128" t="n">
         <v>79.24000000000001</v>
       </c>
-      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6239,7 +6119,6 @@
       <c r="K129" t="n">
         <v>39.125</v>
       </c>
-      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6285,7 +6164,6 @@
       <c r="K130" t="n">
         <v>22.6</v>
       </c>
-      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6331,7 +6209,6 @@
       <c r="K131" t="n">
         <v>67.05</v>
       </c>
-      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6377,7 +6254,6 @@
       <c r="K132" t="n">
         <v>93</v>
       </c>
-      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6423,7 +6299,6 @@
       <c r="K133" t="n">
         <v>11.2</v>
       </c>
-      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6469,7 +6344,6 @@
       <c r="K134" t="n">
         <v>46.8504</v>
       </c>
-      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6515,7 +6389,6 @@
       <c r="K135" t="n">
         <v>2.17</v>
       </c>
-      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6561,7 +6434,6 @@
       <c r="K136" t="n">
         <v>38.19</v>
       </c>
-      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6607,7 +6479,6 @@
       <c r="K137" t="n">
         <v>18.24</v>
       </c>
-      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6653,7 +6524,6 @@
       <c r="K138" t="n">
         <v>19.49</v>
       </c>
-      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6699,7 +6569,6 @@
       <c r="K139" t="n">
         <v>87</v>
       </c>
-      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6745,7 +6614,6 @@
       <c r="K140" t="n">
         <v>7.470000000000001</v>
       </c>
-      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6791,7 +6659,6 @@
       <c r="K141" t="n">
         <v>15.98</v>
       </c>
-      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6837,7 +6704,6 @@
       <c r="K142" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6883,7 +6749,6 @@
       <c r="K143" t="n">
         <v>22.33333</v>
       </c>
-      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6929,7 +6794,6 @@
       <c r="K144" t="n">
         <v>51.8075</v>
       </c>
-      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6975,7 +6839,6 @@
       <c r="K145" t="n">
         <v>298</v>
       </c>
-      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7021,7 +6884,6 @@
       <c r="K146" t="n">
         <v>28</v>
       </c>
-      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7067,7 +6929,6 @@
       <c r="K147" t="n">
         <v>5.6</v>
       </c>
-      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7113,7 +6974,6 @@
       <c r="K148" t="n">
         <v>16.8</v>
       </c>
-      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7159,7 +7019,6 @@
       <c r="K149" t="n">
         <v>11.75</v>
       </c>
-      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7205,7 +7064,6 @@
       <c r="K150" t="n">
         <v>11.09</v>
       </c>
-      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7251,7 +7109,6 @@
       <c r="K151" t="n">
         <v>11.085</v>
       </c>
-      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7297,7 +7154,6 @@
       <c r="K152" t="n">
         <v>9.76</v>
       </c>
-      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7343,7 +7199,6 @@
       <c r="K153" t="n">
         <v>40.3328</v>
       </c>
-      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7389,7 +7244,6 @@
       <c r="K154" t="n">
         <v>8.24</v>
       </c>
-      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7435,7 +7289,6 @@
       <c r="K155" t="n">
         <v>128.421</v>
       </c>
-      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7481,7 +7334,6 @@
       <c r="K156" t="n">
         <v>6.99</v>
       </c>
-      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7527,7 +7379,6 @@
       <c r="K157" t="n">
         <v>99.73</v>
       </c>
-      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7573,7 +7424,6 @@
       <c r="K158" t="n">
         <v>13</v>
       </c>
-      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7619,7 +7469,6 @@
       <c r="K159" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7665,7 +7514,6 @@
       <c r="K160" t="n">
         <v>39.68</v>
       </c>
-      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7711,7 +7559,6 @@
       <c r="K161" t="n">
         <v>24.2</v>
       </c>
-      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7757,7 +7604,6 @@
       <c r="K162" t="n">
         <v>11.98</v>
       </c>
-      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7803,7 +7649,6 @@
       <c r="K163" t="n">
         <v>7.94</v>
       </c>
-      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7849,7 +7694,6 @@
       <c r="K164" t="n">
         <v>86.765</v>
       </c>
-      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7895,7 +7739,6 @@
       <c r="K165" t="n">
         <v>16.18</v>
       </c>
-      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7941,7 +7784,6 @@
       <c r="K166" t="n">
         <v>9.75</v>
       </c>
-      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7987,7 +7829,6 @@
       <c r="K167" t="n">
         <v>5.59</v>
       </c>
-      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8033,7 +7874,6 @@
       <c r="K168" t="n">
         <v>33.68</v>
       </c>
-      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8079,7 +7919,6 @@
       <c r="K169" t="n">
         <v>8.98</v>
       </c>
-      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8172,7 +8011,6 @@
       <c r="K171" t="n">
         <v>52.03</v>
       </c>
-      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8218,7 +8056,6 @@
       <c r="K172" t="n">
         <v>32.3712</v>
       </c>
-      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8264,7 +8101,6 @@
       <c r="K173" t="n">
         <v>48.17</v>
       </c>
-      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8310,7 +8146,6 @@
       <c r="K174" t="n">
         <v>25.575</v>
       </c>
-      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8356,7 +8191,6 @@
       <c r="K175" t="n">
         <v>77.14375000000001</v>
       </c>
-      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8402,7 +8236,6 @@
       <c r="K176" t="n">
         <v>78.054</v>
       </c>
-      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8448,7 +8281,6 @@
       <c r="K177" t="n">
         <v>34.623</v>
       </c>
-      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8494,7 +8326,6 @@
       <c r="K178" t="n">
         <v>29.4768</v>
       </c>
-      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8540,7 +8371,6 @@
       <c r="K179" t="n">
         <v>40.6784</v>
       </c>
-      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8586,7 +8416,6 @@
       <c r="K180" t="n">
         <v>49.1815</v>
       </c>
-      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8632,7 +8461,6 @@
       <c r="K181" t="n">
         <v>37.324</v>
       </c>
-      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8678,7 +8506,6 @@
       <c r="K182" t="n">
         <v>101.745</v>
       </c>
-      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8724,7 +8551,6 @@
       <c r="K183" t="n">
         <v>55.65</v>
       </c>
-      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8770,7 +8596,6 @@
       <c r="K184" t="n">
         <v>35.4816</v>
       </c>
-      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8816,7 +8641,6 @@
       <c r="K185" t="n">
         <v>15.2888</v>
       </c>
-      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8862,7 +8686,6 @@
       <c r="K186" t="n">
         <v>3.45</v>
       </c>
-      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8908,7 +8731,6 @@
       <c r="K187" t="n">
         <v>5.28</v>
       </c>
-      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8954,7 +8776,6 @@
       <c r="K188" t="n">
         <v>11.706667</v>
       </c>
-      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9000,7 +8821,6 @@
       <c r="K189" t="n">
         <v>12.32</v>
       </c>
-      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9046,7 +8866,6 @@
       <c r="K190" t="n">
         <v>16.38</v>
       </c>
-      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9092,7 +8911,6 @@
       <c r="K191" t="n">
         <v>15.94</v>
       </c>
-      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9138,7 +8956,6 @@
       <c r="K192" t="n">
         <v>4.08</v>
       </c>
-      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9184,7 +9001,6 @@
       <c r="K193" t="n">
         <v>12.52</v>
       </c>
-      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9230,7 +9046,6 @@
       <c r="K194" t="n">
         <v>33.11</v>
       </c>
-      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9276,7 +9091,6 @@
       <c r="K195" t="n">
         <v>16.38</v>
       </c>
-      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9322,7 +9136,6 @@
       <c r="K196" t="n">
         <v>5.46</v>
       </c>
-      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9368,7 +9181,6 @@
       <c r="K197" t="n">
         <v>16.38</v>
       </c>
-      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9414,7 +9226,6 @@
       <c r="K198" t="n">
         <v>53.912</v>
       </c>
-      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9460,7 +9271,6 @@
       <c r="K199" t="n">
         <v>348.96</v>
       </c>
-      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9506,7 +9316,6 @@
       <c r="K200" t="n">
         <v>16.38</v>
       </c>
-      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9552,7 +9361,6 @@
       <c r="K201" t="n">
         <v>69.98</v>
       </c>
-      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9598,7 +9406,6 @@
       <c r="K202" t="n">
         <v>17.08</v>
       </c>
-      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9644,7 +9451,6 @@
       <c r="K203" t="n">
         <v>27</v>
       </c>
-      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9790,7 +9596,6 @@
       <c r="K206" t="n">
         <v>73.524</v>
       </c>
-      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9836,7 +9641,6 @@
       <c r="K207" t="n">
         <v>71.10000000000001</v>
       </c>
-      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9882,7 +9686,6 @@
       <c r="K208" t="n">
         <v>28.32</v>
       </c>
-      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9928,7 +9731,6 @@
       <c r="K209" t="n">
         <v>38.34</v>
       </c>
-      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9974,7 +9776,6 @@
       <c r="K210" t="n">
         <v>63.31</v>
       </c>
-      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10020,7 +9821,6 @@
       <c r="K211" t="n">
         <v>51.05</v>
       </c>
-      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10066,7 +9866,6 @@
       <c r="K212" t="n">
         <v>28.15</v>
       </c>
-      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10112,7 +9911,6 @@
       <c r="K213" t="n">
         <v>18.94</v>
       </c>
-      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10158,7 +9956,6 @@
       <c r="K214" t="n">
         <v>28.782</v>
       </c>
-      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10204,7 +10001,6 @@
       <c r="K215" t="n">
         <v>7.18</v>
       </c>
-      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10250,7 +10046,6 @@
       <c r="K216" t="n">
         <v>15.7179</v>
       </c>
-      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10296,7 +10091,6 @@
       <c r="K217" t="n">
         <v>11.945</v>
       </c>
-      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10342,7 +10136,6 @@
       <c r="K218" t="n">
         <v>37.98</v>
       </c>
-      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10388,7 +10181,6 @@
       <c r="K219" t="n">
         <v>9.293334</v>
       </c>
-      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10434,7 +10226,6 @@
       <c r="K220" t="n">
         <v>114.24384</v>
       </c>
-      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10480,7 +10271,6 @@
       <c r="K221" t="n">
         <v>12.200001</v>
       </c>
-      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10526,7 +10316,6 @@
       <c r="K222" t="n">
         <v>54.619998</v>
       </c>
-      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10572,7 +10361,6 @@
       <c r="K223" t="n">
         <v>6.285</v>
       </c>
-      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10618,7 +10406,6 @@
       <c r="K224" t="n">
         <v>23.990004</v>
       </c>
-      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10664,7 +10451,6 @@
       <c r="K225" t="n">
         <v>15.8925</v>
       </c>
-      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10710,7 +10496,6 @@
       <c r="K226" t="n">
         <v>9.744</v>
       </c>
-      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10856,7 +10641,6 @@
       <c r="K229" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10902,7 +10686,6 @@
       <c r="K230" t="n">
         <v>56.81</v>
       </c>
-      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10948,7 +10731,6 @@
       <c r="K231" t="n">
         <v>107.91</v>
       </c>
-      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10994,7 +10776,6 @@
       <c r="K232" t="n">
         <v>28.104165</v>
       </c>
-      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11040,7 +10821,6 @@
       <c r="K233" t="n">
         <v>86.71000000000001</v>
       </c>
-      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11136,7 +10916,6 @@
       <c r="K235" t="n">
         <v>81.2</v>
       </c>
-      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11182,7 +10961,6 @@
       <c r="K236" t="n">
         <v>5.96</v>
       </c>
-      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11228,7 +11006,6 @@
       <c r="K237" t="n">
         <v>21.39</v>
       </c>
-      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11274,7 +11051,6 @@
       <c r="K238" t="n">
         <v>24.62</v>
       </c>
-      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11320,7 +11096,6 @@
       <c r="K239" t="n">
         <v>24.52</v>
       </c>
-      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11366,7 +11141,6 @@
       <c r="K240" t="n">
         <v>21.9</v>
       </c>
-      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11412,7 +11186,6 @@
       <c r="K241" t="n">
         <v>18.16</v>
       </c>
-      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11458,7 +11231,6 @@
       <c r="K242" t="n">
         <v>10.325001</v>
       </c>
-      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11504,7 +11276,6 @@
       <c r="K243" t="n">
         <v>61.71</v>
       </c>
-      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11550,7 +11321,6 @@
       <c r="K244" t="n">
         <v>44.805</v>
       </c>
-      <c r="L244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11596,7 +11366,6 @@
       <c r="K245" t="n">
         <v>182.16</v>
       </c>
-      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11642,7 +11411,6 @@
       <c r="K246" t="n">
         <v>0</v>
       </c>
-      <c r="L246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11688,7 +11456,6 @@
       <c r="K247" t="n">
         <v>0</v>
       </c>
-      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11734,7 +11501,6 @@
       <c r="K248" t="n">
         <v>0</v>
       </c>
-      <c r="L248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11780,7 +11546,6 @@
       <c r="K249" t="n">
         <v>0</v>
       </c>
-      <c r="L249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11826,7 +11591,6 @@
       <c r="K250" t="n">
         <v>0</v>
       </c>
-      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11872,7 +11636,6 @@
       <c r="K251" t="n">
         <v>0</v>
       </c>
-      <c r="L251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11918,7 +11681,6 @@
       <c r="K252" t="n">
         <v>0</v>
       </c>
-      <c r="L252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11964,7 +11726,6 @@
       <c r="K253" t="n">
         <v>0</v>
       </c>
-      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12010,7 +11771,6 @@
       <c r="K254" t="n">
         <v>0</v>
       </c>
-      <c r="L254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12056,7 +11816,6 @@
       <c r="K255" t="n">
         <v>0</v>
       </c>
-      <c r="L255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12102,7 +11861,6 @@
       <c r="K256" t="n">
         <v>0</v>
       </c>
-      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12148,7 +11906,6 @@
       <c r="K257" t="n">
         <v>28.27</v>
       </c>
-      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12194,7 +11951,6 @@
       <c r="K258" t="n">
         <v>137.4</v>
       </c>
-      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12240,7 +11996,6 @@
       <c r="K259" t="n">
         <v>21.53</v>
       </c>
-      <c r="L259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12286,7 +12041,6 @@
       <c r="K260" t="n">
         <v>47.94</v>
       </c>
-      <c r="L260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12332,7 +12086,6 @@
       <c r="K261" t="n">
         <v>23.53</v>
       </c>
-      <c r="L261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12378,7 +12131,6 @@
       <c r="K262" t="n">
         <v>14.915</v>
       </c>
-      <c r="L262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12424,7 +12176,6 @@
       <c r="K263" t="n">
         <v>10.97</v>
       </c>
-      <c r="L263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12470,7 +12221,6 @@
       <c r="K264" t="n">
         <v>32.9</v>
       </c>
-      <c r="L264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12516,7 +12266,6 @@
       <c r="K265" t="n">
         <v>36.693336</v>
       </c>
-      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12562,7 +12311,6 @@
       <c r="K266" t="n">
         <v>41</v>
       </c>
-      <c r="L266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12608,7 +12356,6 @@
       <c r="K267" t="n">
         <v>20.28</v>
       </c>
-      <c r="L267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12654,7 +12401,6 @@
       <c r="K268" t="n">
         <v>15.76</v>
       </c>
-      <c r="L268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12700,7 +12446,6 @@
       <c r="K269" t="n">
         <v>12.71</v>
       </c>
-      <c r="L269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12746,7 +12491,6 @@
       <c r="K270" t="n">
         <v>24.19</v>
       </c>
-      <c r="L270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12792,7 +12536,6 @@
       <c r="K271" t="n">
         <v>190.2687</v>
       </c>
-      <c r="L271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12838,7 +12581,6 @@
       <c r="K272" t="n">
         <v>14.23</v>
       </c>
-      <c r="L272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12884,7 +12626,6 @@
       <c r="K273" t="n">
         <v>15.66</v>
       </c>
-      <c r="L273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12930,7 +12671,6 @@
       <c r="K274" t="n">
         <v>39.12</v>
       </c>
-      <c r="L274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12976,7 +12716,6 @@
       <c r="K275" t="n">
         <v>71.14</v>
       </c>
-      <c r="L275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13022,7 +12761,6 @@
       <c r="K276" t="n">
         <v>15.76</v>
       </c>
-      <c r="L276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13068,7 +12806,6 @@
       <c r="K277" t="n">
         <v>81.92700000000001</v>
       </c>
-      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13164,7 +12901,6 @@
       <c r="K279" t="n">
         <v>3.48</v>
       </c>
-      <c r="L279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13210,7 +12946,6 @@
       <c r="K280" t="n">
         <v>66.82666399999999</v>
       </c>
-      <c r="L280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13256,7 +12991,6 @@
       <c r="K281" t="n">
         <v>83.97</v>
       </c>
-      <c r="L281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13302,7 +13036,6 @@
       <c r="K282" t="n">
         <v>7.879186</v>
       </c>
-      <c r="L282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13348,7 +13081,6 @@
       <c r="K283" t="n">
         <v>115.82</v>
       </c>
-      <c r="L283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13394,7 +13126,6 @@
       <c r="K284" t="n">
         <v>60.945</v>
       </c>
-      <c r="L284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13440,7 +13171,6 @@
       <c r="K285" t="n">
         <v>5.22</v>
       </c>
-      <c r="L285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13486,7 +13216,6 @@
       <c r="K286" t="n">
         <v>187.2</v>
       </c>
-      <c r="L286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13532,7 +13261,6 @@
       <c r="K287" t="n">
         <v>3.48</v>
       </c>
-      <c r="L287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13578,7 +13306,6 @@
       <c r="K288" t="n">
         <v>3.4</v>
       </c>
-      <c r="L288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13624,7 +13351,6 @@
       <c r="K289" t="n">
         <v>23.914546</v>
       </c>
-      <c r="L289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13670,7 +13396,6 @@
       <c r="K290" t="n">
         <v>47.579</v>
       </c>
-      <c r="L290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13716,7 +13441,6 @@
       <c r="K291" t="n">
         <v>11.84</v>
       </c>
-      <c r="L291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13762,7 +13486,6 @@
       <c r="K292" t="n">
         <v>85.69800000000001</v>
       </c>
-      <c r="L292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13808,7 +13531,6 @@
       <c r="K293" t="n">
         <v>120.74167</v>
       </c>
-      <c r="L293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13904,7 +13626,6 @@
       <c r="K295" t="n">
         <v>102.75</v>
       </c>
-      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13950,7 +13671,6 @@
       <c r="K296" t="n">
         <v>58.7</v>
       </c>
-      <c r="L296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13996,7 +13716,6 @@
       <c r="K297" t="n">
         <v>1508.4</v>
       </c>
-      <c r="L297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14042,7 +13761,6 @@
       <c r="K298" t="n">
         <v>48.55</v>
       </c>
-      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14088,7 +13806,6 @@
       <c r="K299" t="n">
         <v>1883.032998</v>
       </c>
-      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14134,7 +13851,6 @@
       <c r="K300" t="n">
         <v>0</v>
       </c>
-      <c r="L300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14180,7 +13896,6 @@
       <c r="K301" t="n">
         <v>18.684</v>
       </c>
-      <c r="L301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14226,7 +13941,6 @@
       <c r="K302" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="L302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14272,7 +13986,6 @@
       <c r="K303" t="n">
         <v>27.0618</v>
       </c>
-      <c r="L303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14318,7 +14031,6 @@
       <c r="K304" t="n">
         <v>48.1272</v>
       </c>
-      <c r="L304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14364,7 +14076,6 @@
       <c r="K305" t="n">
         <v>11.875</v>
       </c>
-      <c r="L305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14410,7 +14121,6 @@
       <c r="K306" t="n">
         <v>21.9</v>
       </c>
-      <c r="L306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14456,7 +14166,6 @@
       <c r="K307" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="L307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14502,7 +14211,6 @@
       <c r="K308" t="n">
         <v>8.94</v>
       </c>
-      <c r="L308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14548,7 +14256,6 @@
       <c r="K309" t="n">
         <v>31.44</v>
       </c>
-      <c r="L309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14594,7 +14301,6 @@
       <c r="K310" t="n">
         <v>15.44</v>
       </c>
-      <c r="L310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14640,7 +14346,6 @@
       <c r="K311" t="n">
         <v>60.49399999999999</v>
       </c>
-      <c r="L311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14686,7 +14391,6 @@
       <c r="K312" t="n">
         <v>27.51</v>
       </c>
-      <c r="L312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14732,7 +14436,6 @@
       <c r="K313" t="n">
         <v>96.42</v>
       </c>
-      <c r="L313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14778,7 +14481,6 @@
       <c r="K314" t="n">
         <v>42.92</v>
       </c>
-      <c r="L314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14824,7 +14526,6 @@
       <c r="K315" t="n">
         <v>43.92</v>
       </c>
-      <c r="L315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14870,7 +14571,6 @@
       <c r="K316" t="n">
         <v>14.3</v>
       </c>
-      <c r="L316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14916,7 +14616,6 @@
       <c r="K317" t="n">
         <v>75.941671</v>
       </c>
-      <c r="L317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14962,7 +14661,6 @@
       <c r="K318" t="n">
         <v>70.100004</v>
       </c>
-      <c r="L318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15008,7 +14706,6 @@
       <c r="K319" t="n">
         <v>36.63</v>
       </c>
-      <c r="L319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15054,7 +14751,6 @@
       <c r="K320" t="n">
         <v>52.575003</v>
       </c>
-      <c r="L320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15100,7 +14796,6 @@
       <c r="K321" t="n">
         <v>49.62</v>
       </c>
-      <c r="L321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15146,7 +14841,6 @@
       <c r="K322" t="n">
         <v>28.03</v>
       </c>
-      <c r="L322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15192,7 +14886,6 @@
       <c r="K323" t="n">
         <v>119.52</v>
       </c>
-      <c r="L323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15238,7 +14931,6 @@
       <c r="K324" t="n">
         <v>48.11</v>
       </c>
-      <c r="L324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15284,7 +14976,6 @@
       <c r="K325" t="n">
         <v>65.03999999999999</v>
       </c>
-      <c r="L325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15330,7 +15021,6 @@
       <c r="K326" t="n">
         <v>44.84</v>
       </c>
-      <c r="L326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15376,7 +15066,6 @@
       <c r="K327" t="n">
         <v>19.667298</v>
       </c>
-      <c r="L327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15422,7 +15111,6 @@
       <c r="K328" t="n">
         <v>29.31</v>
       </c>
-      <c r="L328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15468,7 +15156,6 @@
       <c r="K329" t="n">
         <v>33.92</v>
       </c>
-      <c r="L329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15514,7 +15201,6 @@
       <c r="K330" t="n">
         <v>48.11</v>
       </c>
-      <c r="L330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15560,7 +15246,6 @@
       <c r="K331" t="n">
         <v>25.488</v>
       </c>
-      <c r="L331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15606,7 +15291,6 @@
       <c r="K332" t="n">
         <v>48.11</v>
       </c>
-      <c r="L332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15652,7 +15336,6 @@
       <c r="K333" t="n">
         <v>27.495</v>
       </c>
-      <c r="L333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15698,7 +15381,6 @@
       <c r="K334" t="n">
         <v>59.1</v>
       </c>
-      <c r="L334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15744,7 +15426,6 @@
       <c r="K335" t="n">
         <v>29.96</v>
       </c>
-      <c r="L335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15790,7 +15471,6 @@
       <c r="K336" t="n">
         <v>124.9</v>
       </c>
-      <c r="L336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15836,7 +15516,6 @@
       <c r="K337" t="n">
         <v>11.16</v>
       </c>
-      <c r="L337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15882,7 +15561,6 @@
       <c r="K338" t="n">
         <v>21.2404</v>
       </c>
-      <c r="L338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15928,7 +15606,6 @@
       <c r="K339" t="n">
         <v>75.71000100000001</v>
       </c>
-      <c r="L339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15974,7 +15651,6 @@
       <c r="K340" t="n">
         <v>62.88</v>
       </c>
-      <c r="L340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -16020,7 +15696,6 @@
       <c r="K341" t="n">
         <v>104.4</v>
       </c>
-      <c r="L341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16066,7 +15741,6 @@
       <c r="K342" t="n">
         <v>28.03</v>
       </c>
-      <c r="L342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16112,7 +15786,6 @@
       <c r="K343" t="n">
         <v>39.90000000000001</v>
       </c>
-      <c r="L343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16158,7 +15831,6 @@
       <c r="K344" t="n">
         <v>33.603</v>
       </c>
-      <c r="L344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16204,7 +15876,6 @@
       <c r="K345" t="n">
         <v>29.707</v>
       </c>
-      <c r="L345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16250,7 +15921,6 @@
       <c r="K346" t="n">
         <v>34.95</v>
       </c>
-      <c r="L346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16296,7 +15966,6 @@
       <c r="K347" t="n">
         <v>36.47</v>
       </c>
-      <c r="L347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16342,7 +16011,6 @@
       <c r="K348" t="n">
         <v>173.97</v>
       </c>
-      <c r="L348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16388,7 +16056,6 @@
       <c r="K349" t="n">
         <v>54.25</v>
       </c>
-      <c r="L349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16434,7 +16101,6 @@
       <c r="K350" t="n">
         <v>34.11931999999999</v>
       </c>
-      <c r="L350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16480,7 +16146,6 @@
       <c r="K351" t="n">
         <v>5.766667</v>
       </c>
-      <c r="L351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16526,7 +16191,6 @@
       <c r="K352" t="n">
         <v>3.77</v>
       </c>
-      <c r="L352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16572,7 +16236,6 @@
       <c r="K353" t="n">
         <v>7.83</v>
       </c>
-      <c r="L353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16618,7 +16281,6 @@
       <c r="K354" t="n">
         <v>415.68</v>
       </c>
-      <c r="L354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16664,7 +16326,6 @@
       <c r="K355" t="n">
         <v>507</v>
       </c>
-      <c r="L355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16710,7 +16371,6 @@
       <c r="K356" t="n">
         <v>0</v>
       </c>
-      <c r="L356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16756,7 +16416,6 @@
       <c r="K357" t="n">
         <v>135.21111</v>
       </c>
-      <c r="L357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16802,7 +16461,6 @@
       <c r="K358" t="n">
         <v>17.48</v>
       </c>
-      <c r="L358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16848,7 +16506,6 @@
       <c r="K359" t="n">
         <v>16.7625</v>
       </c>
-      <c r="L359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16894,7 +16551,6 @@
       <c r="K360" t="n">
         <v>41.54</v>
       </c>
-      <c r="L360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -16990,7 +16646,6 @@
       <c r="K362" t="n">
         <v>7.25</v>
       </c>
-      <c r="L362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -17036,7 +16691,6 @@
       <c r="K363" t="n">
         <v>15.15</v>
       </c>
-      <c r="L363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17082,7 +16736,6 @@
       <c r="K364" t="n">
         <v>24.496008</v>
       </c>
-      <c r="L364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17128,7 +16781,6 @@
       <c r="K365" t="n">
         <v>105.515</v>
       </c>
-      <c r="L365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -17174,7 +16826,6 @@
       <c r="K366" t="n">
         <v>43.32</v>
       </c>
-      <c r="L366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -17220,7 +16871,6 @@
       <c r="K367" t="n">
         <v>23.36</v>
       </c>
-      <c r="L367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -17266,7 +16916,6 @@
       <c r="K368" t="n">
         <v>16.75</v>
       </c>
-      <c r="L368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -17312,7 +16961,6 @@
       <c r="K369" t="n">
         <v>36.57</v>
       </c>
-      <c r="L369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -17358,7 +17006,6 @@
       <c r="K370" t="n">
         <v>74.452</v>
       </c>
-      <c r="L370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -17404,7 +17051,6 @@
       <c r="K371" t="n">
         <v>24.98</v>
       </c>
-      <c r="L371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -17450,7 +17096,6 @@
       <c r="K372" t="n">
         <v>23.01</v>
       </c>
-      <c r="L372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -17496,7 +17141,6 @@
       <c r="K373" t="n">
         <v>14.18</v>
       </c>
-      <c r="L373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -17542,7 +17186,6 @@
       <c r="K374" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="L374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17588,7 +17231,6 @@
       <c r="K375" t="n">
         <v>57.6</v>
       </c>
-      <c r="L375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17634,7 +17276,6 @@
       <c r="K376" t="n">
         <v>317.3049</v>
       </c>
-      <c r="L376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17680,7 +17321,6 @@
       <c r="K377" t="n">
         <v>175.069173</v>
       </c>
-      <c r="L377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17726,7 +17366,6 @@
       <c r="K378" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="L378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17772,7 +17411,6 @@
       <c r="K379" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="L379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17818,7 +17456,6 @@
       <c r="K380" t="n">
         <v>17.598</v>
       </c>
-      <c r="L380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -17864,7 +17501,6 @@
       <c r="K381" t="n">
         <v>2.91</v>
       </c>
-      <c r="L381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -17910,7 +17546,6 @@
       <c r="K382" t="n">
         <v>5.210001</v>
       </c>
-      <c r="L382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -17956,7 +17591,6 @@
       <c r="K383" t="n">
         <v>19.065</v>
       </c>
-      <c r="L383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -18002,7 +17636,6 @@
       <c r="K384" t="n">
         <v>15.76</v>
       </c>
-      <c r="L384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -18048,7 +17681,6 @@
       <c r="K385" t="n">
         <v>20.02</v>
       </c>
-      <c r="L385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18094,7 +17726,6 @@
       <c r="K386" t="n">
         <v>10.636</v>
       </c>
-      <c r="L386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18140,7 +17771,6 @@
       <c r="K387" t="n">
         <v>2.589999</v>
       </c>
-      <c r="L387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18186,7 +17816,6 @@
       <c r="K388" t="n">
         <v>5.79</v>
       </c>
-      <c r="L388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -18232,7 +17861,6 @@
       <c r="K389" t="n">
         <v>70.52</v>
       </c>
-      <c r="L389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -18278,7 +17906,6 @@
       <c r="K390" t="n">
         <v>14.5</v>
       </c>
-      <c r="L390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -18324,7 +17951,6 @@
       <c r="K391" t="n">
         <v>27.06</v>
       </c>
-      <c r="L391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -18370,7 +17996,6 @@
       <c r="K392" t="n">
         <v>0</v>
       </c>
-      <c r="L392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -18416,7 +18041,6 @@
       <c r="K393" t="n">
         <v>47.74</v>
       </c>
-      <c r="L393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -18462,7 +18086,6 @@
       <c r="K394" t="n">
         <v>48.93</v>
       </c>
-      <c r="L394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -18558,7 +18181,6 @@
       <c r="K396" t="n">
         <v>70.252</v>
       </c>
-      <c r="L396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -18654,7 +18276,6 @@
       <c r="K398" t="n">
         <v>60.3</v>
       </c>
-      <c r="L398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18700,7 +18321,6 @@
       <c r="K399" t="n">
         <v>67.7</v>
       </c>
-      <c r="L399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18746,7 +18366,6 @@
       <c r="K400" t="n">
         <v>34.7</v>
       </c>
-      <c r="L400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18792,7 +18411,6 @@
       <c r="K401" t="n">
         <v>50.01000000000001</v>
       </c>
-      <c r="L401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18838,7 +18456,6 @@
       <c r="K402" t="n">
         <v>22.04</v>
       </c>
-      <c r="L402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -18884,7 +18501,6 @@
       <c r="K403" t="n">
         <v>67.7</v>
       </c>
-      <c r="L403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -18930,7 +18546,6 @@
       <c r="K404" t="n">
         <v>20.22</v>
       </c>
-      <c r="L404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18976,7 +18591,6 @@
       <c r="K405" t="n">
         <v>35.808335</v>
       </c>
-      <c r="L405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -19022,7 +18636,6 @@
       <c r="K406" t="n">
         <v>0</v>
       </c>
-      <c r="L406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -19068,7 +18681,6 @@
       <c r="K407" t="n">
         <v>90.94799999999999</v>
       </c>
-      <c r="L407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -19114,7 +18726,6 @@
       <c r="K408" t="n">
         <v>77.8</v>
       </c>
-      <c r="L408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -19160,7 +18771,6 @@
       <c r="K409" t="n">
         <v>24.75</v>
       </c>
-      <c r="L409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -19206,7 +18816,6 @@
       <c r="K410" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="L410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -19252,7 +18861,6 @@
       <c r="K411" t="n">
         <v>3135</v>
       </c>
-      <c r="L411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -19298,7 +18906,6 @@
       <c r="K412" t="n">
         <v>73.86</v>
       </c>
-      <c r="L412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -19344,7 +18951,6 @@
       <c r="K413" t="n">
         <v>85.02</v>
       </c>
-      <c r="L413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -19390,7 +18996,6 @@
       <c r="K414" t="n">
         <v>130.5</v>
       </c>
-      <c r="L414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -19436,7 +19041,6 @@
       <c r="K415" t="n">
         <v>109.68</v>
       </c>
-      <c r="L415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -19482,7 +19086,6 @@
       <c r="K416" t="n">
         <v>76.75</v>
       </c>
-      <c r="L416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -19528,7 +19131,6 @@
       <c r="K417" t="n">
         <v>107.094</v>
       </c>
-      <c r="L417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -19574,7 +19176,6 @@
       <c r="K418" t="n">
         <v>28.2</v>
       </c>
-      <c r="L418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -19620,7 +19221,6 @@
       <c r="K419" t="n">
         <v>97.44</v>
       </c>
-      <c r="L419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -19666,7 +19266,6 @@
       <c r="K420" t="n">
         <v>278.58</v>
       </c>
-      <c r="L420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -19712,7 +19311,6 @@
       <c r="K421" t="n">
         <v>61.01199999999999</v>
       </c>
-      <c r="L421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -19758,7 +19356,6 @@
       <c r="K422" t="n">
         <v>0</v>
       </c>
-      <c r="L422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -19804,7 +19401,6 @@
       <c r="K423" t="n">
         <v>128.84</v>
       </c>
-      <c r="L423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -19850,7 +19446,6 @@
       <c r="K424" t="n">
         <v>237.384</v>
       </c>
-      <c r="L424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -19896,7 +19491,6 @@
       <c r="K425" t="n">
         <v>24.47</v>
       </c>
-      <c r="L425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -19942,7 +19536,6 @@
       <c r="K426" t="n">
         <v>19.24</v>
       </c>
-      <c r="L426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -19988,7 +19581,6 @@
       <c r="K427" t="n">
         <v>29.56</v>
       </c>
-      <c r="L427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -20034,7 +19626,6 @@
       <c r="K428" t="n">
         <v>308.67</v>
       </c>
-      <c r="L428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -20080,7 +19671,6 @@
       <c r="K429" t="n">
         <v>18.27</v>
       </c>
-      <c r="L429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -20126,7 +19716,6 @@
       <c r="K430" t="n">
         <v>29.56</v>
       </c>
-      <c r="L430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20172,7 +19761,6 @@
       <c r="K431" t="n">
         <v>18.42</v>
       </c>
-      <c r="L431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20218,7 +19806,6 @@
       <c r="K432" t="n">
         <v>53.832</v>
       </c>
-      <c r="L432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -20264,7 +19851,6 @@
       <c r="K433" t="n">
         <v>3.7</v>
       </c>
-      <c r="L433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -20360,7 +19946,6 @@
       <c r="K435" t="n">
         <v>20.6336</v>
       </c>
-      <c r="L435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -20406,7 +19991,6 @@
       <c r="K436" t="n">
         <v>709.428</v>
       </c>
-      <c r="L436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -20452,7 +20036,6 @@
       <c r="K437" t="n">
         <v>291.000003</v>
       </c>
-      <c r="L437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -20498,7 +20081,6 @@
       <c r="K438" t="n">
         <v>18.27</v>
       </c>
-      <c r="L438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -20544,7 +20126,6 @@
       <c r="K439" t="n">
         <v>17.4</v>
       </c>
-      <c r="L439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -20590,7 +20171,6 @@
       <c r="K440" t="n">
         <v>29.75001</v>
       </c>
-      <c r="L440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -20636,7 +20216,6 @@
       <c r="K441" t="n">
         <v>13.77</v>
       </c>
-      <c r="L441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -20682,7 +20261,6 @@
       <c r="K442" t="n">
         <v>28.912</v>
       </c>
-      <c r="L442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -20728,7 +20306,6 @@
       <c r="K443" t="n">
         <v>116.518</v>
       </c>
-      <c r="L443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -20774,7 +20351,6 @@
       <c r="K444" t="n">
         <v>137.22</v>
       </c>
-      <c r="L444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20820,7 +20396,6 @@
       <c r="K445" t="n">
         <v>44.655</v>
       </c>
-      <c r="L445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -20866,7 +20441,6 @@
       <c r="K446" t="n">
         <v>325.631423</v>
       </c>
-      <c r="L446" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21212,7 +20786,6 @@
       <c r="G5" t="n">
         <v>3135</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -21276,7 +20849,6 @@
       <c r="G7" t="n">
         <v>1883.032998</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -21306,7 +20878,6 @@
       <c r="G8" t="n">
         <v>1508.4</v>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -21404,7 +20975,6 @@
       <c r="G11" t="n">
         <v>709.428</v>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21502,7 +21072,6 @@
       <c r="G14" t="n">
         <v>507</v>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21532,7 +21101,6 @@
       <c r="G15" t="n">
         <v>415.68</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21562,7 +21130,6 @@
       <c r="G16" t="n">
         <v>399.96</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21592,7 +21159,6 @@
       <c r="G17" t="n">
         <v>386.1</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21622,7 +21188,6 @@
       <c r="G18" t="n">
         <v>348.96</v>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21652,7 +21217,6 @@
       <c r="G19" t="n">
         <v>325.631423</v>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21682,7 +21246,6 @@
       <c r="G20" t="n">
         <v>317.866665</v>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21712,7 +21275,6 @@
       <c r="G21" t="n">
         <v>317.3049</v>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21742,7 +21304,6 @@
       <c r="G22" t="n">
         <v>308.67</v>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21772,7 +21333,6 @@
       <c r="G23" t="n">
         <v>298</v>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -38223,7 +37783,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -40189,4 +39748,3608 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>86 códigos comprados de mais de um fornecedor: custo usado (compra mais recente) x custo máximo já pago. Ordenado pela maior diferença de valor em estoque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nº linhas (fornecedores)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estoque disponível</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Custo mínimo já pago</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Custo máximo já pago</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Custo usado (mais recente)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Data compra mais recente</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Valor em estoque (custo usado)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Valor em estoque (custo máximo)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Diferença (máximo - usado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>22924</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PARAFUSO PONTA BROCA 12 - 5,5MM X 1/2 SEXT (CHAVE 5/16) C/ ARRUELA VILA</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1360</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1335.38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22114</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TIJOLO 6 FUROS 09 X 14 X 24 CER. LORENZETTI</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2514</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1508.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2436.07</v>
+      </c>
+      <c r="K5" t="n">
+        <v>927.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20250</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TIJOLO 6 FUROS 09 X 14 X 29 CER. LORENZETTI</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2598</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1883.03</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2779.86</v>
+      </c>
+      <c r="K6" t="n">
+        <v>896.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CABO DE ACO PLASTIFICADO 3/32" 2,40MM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.4793</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>247.93</v>
+      </c>
+      <c r="J7" t="n">
+        <v>700</v>
+      </c>
+      <c r="K7" t="n">
+        <v>452.07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PRD00045</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CIMENTO SUPREMO 50KG</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>95</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33</v>
+      </c>
+      <c r="F8" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3135</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3505.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>370.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>21571</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COLETE REFLETIVO "XG" AMARELO 10.01.2.3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.622</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>78.48999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>78.48999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRD00017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ESTRIBO DE ACO 07 x 14cm</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>119</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="J10" t="n">
+        <v>113.94</v>
+      </c>
+      <c r="K10" t="n">
+        <v>72.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20530</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MASSA POLIMÉRICA 5KG</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>258</v>
+      </c>
+      <c r="K11" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ARGAMASSA MASSA REBOCO CINZA 20KG</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.522</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.522</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="K12" t="n">
+        <v>63.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20357</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VALVULA CLICK 1.1/4" CORPO PLASTICO TAMPA INOX</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17.9067</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="K13" t="n">
+        <v>53.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22582</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KIT ACESSORIOS BANHEIRO BASICO 5PÇ CROMADO BELLA ARTE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="J14" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22943</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CILINDRO GAS MAPP PRO 400GR</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="J15" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="K15" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>APLICADOR DE SILICONE E PU PROFISSIONAL 9" FERTAK</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="K16" t="n">
+        <v>48.66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20336</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Concreto pronto 20kg</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>107.91</v>
+      </c>
+      <c r="J17" t="n">
+        <v>155.61</v>
+      </c>
+      <c r="K17" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20912</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FERRO 5/16 (12 METROS) 8MM</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="G18" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>298</v>
+      </c>
+      <c r="J18" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ESCORA DE EUCALIPTO</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>36</v>
+      </c>
+      <c r="K19" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20608</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>REBOLO DESBASTE DIAMANTADO 4.1/2 115MM M14 TURBO VILA</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="G20" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>131.52</v>
+      </c>
+      <c r="K20" t="n">
+        <v>34.08</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>21588</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FITA DUPLA FACE 12MMX2MT</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CURVA SOLDAVEL 90° 32MM FORTLEV</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.332</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.332</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="J22" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25.47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CAIXA GORDURA 42L C/CESTO LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27.495</v>
+      </c>
+      <c r="F23" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>27.495</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22957</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FACAO 20 CABO PVC 50CM FERTAK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="F24" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="K24" t="n">
+        <v>18.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>38087</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FITA VEDA ROSCA 18MMX10M QUALIFLON</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="J25" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="K25" t="n">
+        <v>18.04</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>21503</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VALVULA PIA INOX 3.1/2 C/PINO TAMPA INOS PADOVA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="J26" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>16.58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>21486</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MANGUEIRA ENTRADA MAQUINA 1,20M</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.765</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10.765</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="J27" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="K27" t="n">
+        <v>16.29</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>21145</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PILHA ALCALINA AAA C/02 UND ELETRONIC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>22932</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FITA DUPLA FACE 25MMX2M EXTERNO</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>22682</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>REGISTRO DE ESFERA MAQUINA DE LAVAR 1/2"X3/4" FERTAK</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14.4133</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="J30" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="K30" t="n">
+        <v>14.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SAPATO MONODENSIDADE S/BICO CANO BAIXO N°41</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="F31" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="G31" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>106.71</v>
+      </c>
+      <c r="K31" t="n">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SAPATO MONODENSIDADE S/BICO CANO BAIXO N°40</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="F32" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>106.71</v>
+      </c>
+      <c r="K32" t="n">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20803</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CONVERTEDOR FERRUGEM TF7 100ML</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.845</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="K33" t="n">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FITA CREPE USO GERAL BEGE EURO 18MM X 50M</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>21452</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TUBO ESGOTO 100MM - 6M</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>58.918</v>
+      </c>
+      <c r="F35" t="n">
+        <v>59.992</v>
+      </c>
+      <c r="G35" t="n">
+        <v>59.119</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>709.4299999999999</v>
+      </c>
+      <c r="J35" t="n">
+        <v>719.9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20352</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CALKOR 1L  (CAL LIQUIDO)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5.6208</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5.6208</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>22580</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VALVULA LAVATORIO S/LAD S/UNHO 7/8" PLASTICO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20718</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ESPUMA EXPANSIVA 500ML 320G TEKBOND</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>13.5211</v>
+      </c>
+      <c r="F38" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="G38" t="n">
+        <v>13.5211</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>135.21</v>
+      </c>
+      <c r="J38" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20990</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ARAME RECOZIDO N 18</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.972</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DESEMPENADEIRA PLASTICA ESTRIADA 14X27 GERPLAST</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="J40" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="K40" t="n">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>22043</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PILHA ALCALINA AA C/02 UND ELETRONIC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="J41" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>21454</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TUBO SOLDAVEL 25MM - 6M</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>14</v>
+      </c>
+      <c r="F42" t="n">
+        <v>16.504</v>
+      </c>
+      <c r="G42" t="n">
+        <v>15.4288</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="J42" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>23452</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SAPATO MONODENSIDADE S/BICO CANO BAIXO N°42</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="F43" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="G43" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="J43" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>21501</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JOELHO 90 ESGOTO 40MM FORTLEV</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>26</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="J44" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ROLO LA S/ RESPINGO 09CM COM CABO ROMA</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.672</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="J45" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DISCO SERRA/MADEIRA CIRCULAR VIDEA 7. 1/4 24D x 185MM</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>14.915</v>
+      </c>
+      <c r="F46" t="n">
+        <v>17.675</v>
+      </c>
+      <c r="G46" t="n">
+        <v>14.915</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="J46" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>22687</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ABRACADEIRA BORBOLETA 16MM METALMATRIX</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.956</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.956</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="J47" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>21453</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TUBO SOLDAVEL 20MM - 6M</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.009</v>
+      </c>
+      <c r="F48" t="n">
+        <v>13.385</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13.009</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="J48" t="n">
+        <v>80.31</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>22953</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DESEMPENADEIRA DENTA CB PLASTICO 25,5X12CM CABO PLASTICO</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="G49" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="J49" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DUREPOXI 50G</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.8567</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14283</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ABRACADEIRA TIPO U 3/4 BRANCA CLICK</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>50</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>27</v>
+      </c>
+      <c r="J51" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>COLHER PEDREIRO 08 REDONDA</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.575</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="G52" t="n">
+        <v>7.575</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="J52" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20665</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FITA DUPLA FACE 12mm x 2m VILA</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.4417</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.4417</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="J53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SIFAO TUBO EXTENSIVEL BRANCO 72CM PLASBOHN</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="J54" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>22060</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CRUZETA / ESPACADOR 3,00MM C/100</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>22068</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CRUZETA / ESPACADOR 5,00MM C/100</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>21940</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CRUZETA / ESPACADOR 2,00MM C/100</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TORNEIRA JARDIM PRETO</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>11</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.9542</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1624</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FITA ISOLANTE AUTOFUSAO 05M X 19MM PRETA FOXLUX</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="G59" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="J59" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CAIXA MEDIDOR PROVISORIA PRETA</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F60" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="G60" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="J60" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1446</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LUVA ESG SN DN 75 FORTLEV</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>13</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.435</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.435</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="J61" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PU 40 CINZA 380G ORBI QUIMICA</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7.4562</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8.353300000000001</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.353300000000001</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="J62" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ADAPTADOR SOLD CX DAGUA 25X3/4</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>23</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4.906</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.066</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5.066</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>116.52</v>
+      </c>
+      <c r="J63" t="n">
+        <v>116.52</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PREGO POLIDO 17X27 1KG CABECA DUPLA GERDAU - 117000253</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="G64" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J64" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PREGO POLIDO 17X27 1KG COM CABECA</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G65" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MANTA TERMICA SIMPLES 1 FACE 1,20M - METRO</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="J66" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20452</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ROLO LA S/RESPINGO S/CABO 23CM ROMA</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="J67" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20596</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HASTE P/CHUVEIRO BRANCA 1/2" 30CM HERC</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5.5875</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.5875</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="J68" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>21435</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FITA CREPE AMARELA 18X40 AUTOMOTIVA</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="J69" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>21152</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TRENA EMBORRACHADA 10M X 25MM THOMPSON</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="G70" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="J70" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20674</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SAPATO MONODENSIDADE S/BICO CANO BAIXO N°43</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="F71" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="G71" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="J71" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20734</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TORNEIRA JARDIM MEGAJATO 1/2" AMARELA  - METRO</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>93</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.0459</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.0459</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>190.27</v>
+      </c>
+      <c r="J72" t="n">
+        <v>190.27</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20962</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PROTETOR AUDITIVO/AURICULAR C/ CORDAO</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="J73" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>21989</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OCULOS BOXER VERDE VONDER</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>12</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3.618</v>
+      </c>
+      <c r="F74" t="n">
+        <v>5.8417</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5.8417</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="J74" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>21665</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JOELHO ESGOTO 90.X100MM 0619</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>21582</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ABRACADEIRA NYLON PRETA 4,8 X 370 - 100PÇS VILA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="F76" t="n">
+        <v>13.478</v>
+      </c>
+      <c r="G76" t="n">
+        <v>13.478</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="J76" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>22922</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DESEMPENADEIRA LISA CB PLASTICO 12x25,5CM</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F77" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="G77" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>22146</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TRINCHA BRANCA "396" 3.0"  396/7</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>6</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="G78" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="J78" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>22144</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TRINCHA BRANCA "396" 1.1/2"  396/4</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="J79" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CANALETA ADESIVA COM DIVISORIA 20X10X2000MM BRANCA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>54</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4.396</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4.396</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>237.38</v>
+      </c>
+      <c r="J80" t="n">
+        <v>237.38</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>22583</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TORNEIRA DE BOIA P/CX DAGUA ALTA VAZAO 1/2 E 3/4" CIPLA</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="G81" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="J81" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>22686</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CARRINHO DE CARGA 45 L MINASUL</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="G82" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>278.58</v>
+      </c>
+      <c r="J82" t="n">
+        <v>278.58</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>31329</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BLOCO ESPUMA MULTIUSO AMARELO</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>22956</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LIXA FERRO GR80 225X275</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>29</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="J84" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>23454</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAPATO MONODENSIDADE S/BICO N°39</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="F85" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="G85" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J85" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PLUG PINO MACHO 2P+T 10A/250V</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3.8525</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5.2975</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5.2975</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="J86" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>643882</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LIXA MASSA MADEIRA GR80 225X275</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>66</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="J87" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TANQUE PLASTICO BRANCO 26L C/ VALVULA FIBERBLU</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="F88" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="G88" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="J88" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PRD00065</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PU 40 BRANCO 380G</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>19</v>
+      </c>
+      <c r="E89" t="n">
+        <v>7.4467</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9.2142</v>
+      </c>
+      <c r="G89" t="n">
+        <v>9.2142</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>175.07</v>
+      </c>
+      <c r="J89" t="n">
+        <v>175.07</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Operacional/clientes/hora-z/outputs/09-2026/Arquivos/15-inteligencia-dados-estoque-giro-margem_snapshot-2026-09-15.xlsx
+++ b/Operacional/clientes/hora-z/outputs/09-2026/Arquivos/15-inteligencia-dados-estoque-giro-margem_snapshot-2026-09-15.xlsx
@@ -20453,13 +20453,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Valor em estoque a custo por categoria, bruto e excluindo os 16 SKUs com outlier de cadastro (custo cadastrado acima do preço de venda, ver aba "Auditoria outliers cadastro"). Mesmo tratamento já dado ao faturamento com os lançamentos "Plataforma": o valor bruto por categoria está inflado nesses SKUs, então a leitura "sem outliers" é a recomendada para decisão de estoque.</t>
+          <t>Valor em estoque a custo por categoria, bruto e excluindo os 16 SKUs com outlier de cadastro (custo cadastrado acima do preco de venda, ver aba "Auditoria outliers cadastro"). Mesmo tratamento ja dado ao faturamento com os lancamentos "Plataforma": o valor bruto por categoria esta inflado nesses SKUs, entao a leitura "sem outliers" e a recomendada para decisao de estoque. ATUALIZADO EM 18/09/2026: colunas F a H acrescentam, por categoria, quantos SKUs (dos 86 do total do cliente) foram comprados de mais de um fornecedor a custos diferentes e qual seria o valor em estoque desses SKUs especificos no cenario de custo minimo e no cenario de custo maximo ja registrados. E uma leitura a mais, nao substitui as colunas B a E (que continuam usando o custo da compra mais recente para todo o restante do estoque).</t>
         </is>
       </c>
     </row>
@@ -20489,6 +20489,21 @@
           <t>Valor em estoque a custo (sem outliers)</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SKUs c/ múltiplos fornecedores</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Valor em estoque desses SKUs (custo mín.)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Valor em estoque desses SKUs (custo máx.)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20508,6 +20523,15 @@
       <c r="E4" t="n">
         <v>10934.676253</v>
       </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7465.94</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10667.13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20527,6 +20551,15 @@
       <c r="E5" t="n">
         <v>6140.383269000001</v>
       </c>
+      <c r="F5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1576.11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2211.68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20546,6 +20579,15 @@
       <c r="E6" t="n">
         <v>2807.956863000001</v>
       </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>204.19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1963.75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20565,6 +20607,15 @@
       <c r="E7" t="n">
         <v>2990.604075000001</v>
       </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="H7" t="n">
+        <v>520.52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20584,6 +20635,15 @@
       <c r="E8" t="n">
         <v>1578.526181</v>
       </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>378.97</v>
+      </c>
+      <c r="H8" t="n">
+        <v>568.73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20603,6 +20663,15 @@
       <c r="E9" t="n">
         <v>1640.404</v>
       </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>69.86</v>
+      </c>
+      <c r="H9" t="n">
+        <v>115.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20622,6 +20691,15 @@
       <c r="E10" t="n">
         <v>1604.654277</v>
       </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>390.43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>452.27</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20641,6 +20719,15 @@
       <c r="E11" t="n">
         <v>761.9066780000001</v>
       </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>159.75</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20659,6 +20746,9 @@
       </c>
       <c r="E12" t="n">
         <v>15.66</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20672,13 +20762,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Top 20 produtos por valor em estoque a custo, bruto (coluna com flag de outlier de cadastro) e Top 15 recalculado excluindo os outliers de cadastro (custo &gt; preço de venda cadastrado), que distorcem a leitura de onde está o capital parado. Ex: bucha plástica c/ anel concreto 8mm (código 22483) tem custo cadastrado de R$ 11,25 x 478 unidades = R$ 5.377,50 no bruto, mas o preço de venda cadastrado é R$ 0,05, ou seja, o custo está claramente errado.</t>
+          <t>Top 20 produtos por valor em estoque a custo, bruto (coluna com flag de outlier de cadastro) e Top 15 recalculado excluindo os outliers de cadastro (custo &gt; preco de venda cadastrado), que distorcem a leitura de onde esta o capital parado. Ex: bucha plastica c/ anel concreto 8mm (codigo 22483) tem custo cadastrado de R$ 11,25 x 478 unidades = R$ 5.377,50 no bruto, mas o preco de venda cadastrado e R$ 0,05, ou seja, o custo esta claramente errado. ATUALIZADO EM 18/09/2026: agrupamento por produto (codigo) continua o mesmo, mas as colunas I a M mostram, para os produtos comprados de mais de um fornecedor a custos diferentes, o custo e o valor em estoque no cenario minimo e no cenario maximo lado a lado, em vez de uma unica escolha de custo. Produto com uma so linha de compra fica com essas colunas em branco (sem ambiguidade a resolver).</t>
         </is>
       </c>
     </row>
@@ -20721,6 +20811,31 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>Outlier de cadastro</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nº fornecedores (custos distintos)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Custo mín. já pago</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Custo máx. já pago</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Valor em estoque (custo mín.)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Valor em estoque (custo máx.)</t>
         </is>
       </c>
     </row>
@@ -20786,6 +20901,21 @@
       <c r="G5" t="n">
         <v>3135</v>
       </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3135</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3505.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -20849,6 +20979,21 @@
       <c r="G7" t="n">
         <v>1883.032998</v>
       </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1883.03</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2779.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -20878,6 +21023,21 @@
       <c r="G8" t="n">
         <v>1508.4</v>
       </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1508.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2436.07</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -20975,6 +21135,21 @@
       <c r="G11" t="n">
         <v>709.428</v>
       </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.918</v>
+      </c>
+      <c r="K11" t="n">
+        <v>59.992</v>
+      </c>
+      <c r="L11" t="n">
+        <v>707.02</v>
+      </c>
+      <c r="M11" t="n">
+        <v>719.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21333,6 +21508,21 @@
       <c r="G23" t="n">
         <v>298</v>
       </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="L23" t="n">
+        <v>298</v>
+      </c>
+      <c r="M23" t="n">
+        <v>339.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21375,6 +21565,31 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>Valor em estoque a custo</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nº fornecedores (custos distintos)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Custo mín. já pago</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Custo máx. já pago</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Valor em estoque (custo mín.)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Valor em estoque (custo máx.)</t>
         </is>
       </c>
     </row>
@@ -21406,6 +21621,21 @@
       <c r="G27" t="n">
         <v>3135</v>
       </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>33</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3135</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3505.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -21435,6 +21665,21 @@
       <c r="G28" t="n">
         <v>1883.032998</v>
       </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1883.03</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2779.86</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -21464,6 +21709,21 @@
       <c r="G29" t="n">
         <v>1508.4</v>
       </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1508.4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2436.07</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -21493,6 +21753,21 @@
       <c r="G30" t="n">
         <v>709.428</v>
       </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>58.918</v>
+      </c>
+      <c r="K30" t="n">
+        <v>59.992</v>
+      </c>
+      <c r="L30" t="n">
+        <v>707.02</v>
+      </c>
+      <c r="M30" t="n">
+        <v>719.9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -21782,6 +22057,21 @@
       </c>
       <c r="G40" t="n">
         <v>298</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="K40" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="L40" t="n">
+        <v>298</v>
+      </c>
+      <c r="M40" t="n">
+        <v>339.5</v>
       </c>
     </row>
     <row r="41">
@@ -22462,7 +22752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:N298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22473,12 +22763,18 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Quadrantes definidos pela mediana do próprio grupo cruzado (295 SKUs presentes nos dois relatórios): giro &gt;= 4 un. = alto giro; margem &gt;= 44,3% = alta margem. Estrela = alto giro/alta margem. Isca = alto giro/baixa margem. Reserva de lucro = baixo giro/alta margem. Candidato a liquidar = baixo giro/baixa margem.</t>
+          <t>Quadrantes definidos pela mediana do proprio grupo cruzado (295 SKUs presentes nos dois relatorios): giro &gt;= 4 un. = alto giro; margem &gt;= 44,3% = alta margem. Estrela = alto giro/alta margem. Isca = alto giro/baixa margem. Reserva de lucro = baixo giro/alta margem. Candidato a liquidar = baixo giro/baixa margem. ATUALIZADO EM 18/09/2026: colunas I a N mostram, para os 77 SKUs desta lista comprados de mais de um fornecedor a custos diferentes, a margem e o quadrante recalculados no cenario de custo minimo e no cenario de custo maximo ja registrados. Coluna N sinaliza quando o quadrante muda de lado (alta/baixa margem) dependendo do custo, ou seja, quando a classificacao Estrela/Isca/Reserva de lucro/Candidato a liquidar deste produto especifico e provisoria ate o cliente confirmar qual custo vale. O giro nao muda entre os cenarios (fisicamente e o mesmo estoque, so o custo de aquisicao varia). Produto com uma so linha de compra fica com essas colunas em branco.</t>
         </is>
       </c>
     </row>
@@ -22523,6 +22819,36 @@
           <t>Quadrante</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Nº fornecedores (custos distintos)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Margem % (custo mín.)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Margem % (custo máx.)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Quadrante (custo mín.)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Quadrante (custo máx.)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Classificação provisória (múltiplos fornecedores)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22559,6 +22885,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22595,6 +22945,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22631,6 +23005,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22667,6 +23065,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22739,6 +23161,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-250</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22955,6 +23401,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23063,6 +23533,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23243,6 +23737,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>27</v>
+      </c>
+      <c r="K23" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -23423,6 +23941,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23495,6 +24037,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -23675,6 +24241,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>50</v>
+      </c>
+      <c r="K35" t="n">
+        <v>42</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -23747,6 +24337,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -23891,6 +24505,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -23999,6 +24637,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24107,6 +24769,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -24287,6 +24973,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="K52" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24395,6 +25105,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="n">
+        <v>49</v>
+      </c>
+      <c r="K55" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -24431,6 +25165,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="K56" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -24575,6 +25333,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>100</v>
+      </c>
+      <c r="K60" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -24683,6 +25465,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>100</v>
+      </c>
+      <c r="K63" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -24791,6 +25597,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>40</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -25007,6 +25837,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -25043,6 +25897,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -25223,6 +26101,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -25259,6 +26161,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -25367,6 +26293,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25403,6 +26353,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I83" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="K83" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -25511,6 +26485,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I86" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="K86" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -25547,6 +26545,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="K87" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -25655,6 +26677,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>100</v>
+      </c>
+      <c r="K90" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -25727,6 +26773,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="K92" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25871,6 +26941,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I96" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K96" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -25979,6 +27073,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I99" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>64</v>
+      </c>
+      <c r="K99" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -26087,6 +27205,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="K102" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -26123,6 +27265,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I103" t="n">
+        <v>2</v>
+      </c>
+      <c r="J103" t="n">
+        <v>100</v>
+      </c>
+      <c r="K103" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -26159,6 +27325,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K104" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -26267,6 +27457,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>100</v>
+      </c>
+      <c r="K107" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -26411,6 +27625,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I111" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="K111" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -26519,6 +27757,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I114" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" t="n">
+        <v>100</v>
+      </c>
+      <c r="K114" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -26627,6 +27889,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I117" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="K117" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -26843,6 +28129,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I123" t="n">
+        <v>3</v>
+      </c>
+      <c r="J123" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="K123" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -27023,6 +28333,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="K128" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -27167,6 +28501,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I132" t="n">
+        <v>2</v>
+      </c>
+      <c r="J132" t="n">
+        <v>100</v>
+      </c>
+      <c r="K132" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -27275,6 +28633,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I135" t="n">
+        <v>2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -27419,6 +28801,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>100</v>
+      </c>
+      <c r="K139" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -27599,6 +29005,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I144" t="n">
+        <v>3</v>
+      </c>
+      <c r="J144" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K144" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -28031,6 +29461,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I156" t="n">
+        <v>2</v>
+      </c>
+      <c r="J156" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="K156" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -28247,6 +29701,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I162" t="n">
+        <v>2</v>
+      </c>
+      <c r="J162" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -28283,6 +29761,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I163" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" t="n">
+        <v>70</v>
+      </c>
+      <c r="K163" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -28319,6 +29821,30 @@
           <t>ISCA</t>
         </is>
       </c>
+      <c r="I164" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="K164" t="n">
+        <v>38</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>ISCA</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -28391,6 +29917,30 @@
           <t>ESTRELA</t>
         </is>
       </c>
+      <c r="I166" t="n">
+        <v>2</v>
+      </c>
+      <c r="J166" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="K166" t="n">
+        <v>53</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>ESTRELA</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -28571,6 +30121,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I171" t="n">
+        <v>2</v>
+      </c>
+      <c r="J171" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K171" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -28607,6 +30181,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I172" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="K172" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -28643,6 +30241,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I173" t="n">
+        <v>2</v>
+      </c>
+      <c r="J173" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="K173" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -28967,6 +30589,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I182" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K182" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -29003,6 +30649,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I183" t="n">
+        <v>2</v>
+      </c>
+      <c r="J183" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K183" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -29111,6 +30781,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I186" t="n">
+        <v>2</v>
+      </c>
+      <c r="J186" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K186" t="n">
+        <v>-133.4</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -29399,6 +31093,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I194" t="n">
+        <v>2</v>
+      </c>
+      <c r="J194" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>14</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -29435,6 +31153,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I195" t="n">
+        <v>2</v>
+      </c>
+      <c r="J195" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="K195" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -29543,6 +31285,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I198" t="n">
+        <v>2</v>
+      </c>
+      <c r="J198" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="K198" t="n">
+        <v>45</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -29795,6 +31561,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I205" t="n">
+        <v>2</v>
+      </c>
+      <c r="J205" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-285.9</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -29867,6 +31657,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I207" t="n">
+        <v>2</v>
+      </c>
+      <c r="J207" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="K207" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -29939,6 +31753,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I209" t="n">
+        <v>2</v>
+      </c>
+      <c r="J209" t="n">
+        <v>100</v>
+      </c>
+      <c r="K209" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -30119,6 +31957,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I214" t="n">
+        <v>2</v>
+      </c>
+      <c r="J214" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="K214" t="n">
+        <v>24</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -30479,6 +32341,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I224" t="n">
+        <v>2</v>
+      </c>
+      <c r="J224" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K224" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -30875,6 +32761,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I235" t="n">
+        <v>2</v>
+      </c>
+      <c r="J235" t="n">
+        <v>100</v>
+      </c>
+      <c r="K235" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -31055,6 +32965,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I240" t="n">
+        <v>2</v>
+      </c>
+      <c r="J240" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K240" t="n">
+        <v>14</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -31952,6 +33886,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I265" t="n">
+        <v>2</v>
+      </c>
+      <c r="J265" t="n">
+        <v>100</v>
+      </c>
+      <c r="K265" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -32348,6 +34306,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I276" t="n">
+        <v>2</v>
+      </c>
+      <c r="J276" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-2620</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -32384,6 +34366,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I277" t="n">
+        <v>2</v>
+      </c>
+      <c r="J277" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -32420,6 +34426,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I278" t="n">
+        <v>3</v>
+      </c>
+      <c r="J278" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K278" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -32456,6 +34486,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I279" t="n">
+        <v>3</v>
+      </c>
+      <c r="J279" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K279" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -32528,6 +34582,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I281" t="n">
+        <v>2</v>
+      </c>
+      <c r="J281" t="n">
+        <v>43</v>
+      </c>
+      <c r="K281" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -32600,6 +34678,30 @@
           <t>CANDIDATO_A_LIQUIDAR</t>
         </is>
       </c>
+      <c r="I283" t="n">
+        <v>2</v>
+      </c>
+      <c r="J283" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="K283" t="n">
+        <v>35</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -32672,6 +34774,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I285" t="n">
+        <v>2</v>
+      </c>
+      <c r="J285" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="K285" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -32816,6 +34942,30 @@
           <t>RESERVA_DE_LUCRO</t>
         </is>
       </c>
+      <c r="I289" t="n">
+        <v>2</v>
+      </c>
+      <c r="J289" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="K289" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>CANDIDATO_A_LIQUIDAR</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -32850,6 +35000,30 @@
       <c r="H290" t="inlineStr">
         <is>
           <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>2</v>
+      </c>
+      <c r="J290" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="K290" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>RESERVA_DE_LUCRO</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>NAO</t>
         </is>
       </c>
     </row>
@@ -33152,13 +35326,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Proxy de estoque parado: 148 SKUs sem nenhuma venda registrada na Curva ABC recebida (acumulado até 15/09/2026), valor financeiro parado a custo de R$ 6,293.29. Ordenado por Data da Última Compra (mais antigo primeiro), não por valor: 8 dos 148 SKUs não têm essa data preenchida no relatório de Estoque (ficam ao final da lista, sem posição de antiguidade). "Data da última compra" é quando a LOJA comprou do fornecedor, não quando o cliente final comprou o produto: não é régua de tempo parado por venda de verdade, é a leitura mais honesta possível com o dado disponível. CORRIGIDO EM 18/09/2026: rodada anterior estava ordenada por valor, não por antiguidade.</t>
+          <t>Proxy de estoque parado: 148 SKUs sem nenhuma venda registrada na Curva ABC recebida (acumulado ate 15/09/2026), valor financeiro parado a custo de R$ 6.293,29. Ordenado por Data da Ultima Compra (mais antigo primeiro), nao por valor: 8 dos 148 SKUs nao tem essa data preenchida no relatorio de Estoque (ficam ao final da lista, sem posicao de antiguidade). "Data da ultima compra" e quando a LOJA comprou do fornecedor, nao quando o cliente final comprou o produto: nao e regua de tempo parado por venda de verdade, e a leitura mais honesta possivel com o dado disponivel. CORRIGIDO EM 18/09/2026: rodada anterior estava ordenada por valor, nao por antiguidade. ATUALIZADO EM 18/09/2026: colunas H a K mostram, para os 9 destes 148 SKUs comprados de mais de um fornecedor a custos diferentes, o custo e o valor parado no cenario minimo e no cenario maximo lado a lado. Produto com uma so linha de compra fica com essas colunas em branco.</t>
         </is>
       </c>
     </row>
@@ -33196,6 +35370,26 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>Valor parado a custo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Custo mín. já pago</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Custo máx. já pago</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Valor parado (custo mín.)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Valor parado (custo máx.)</t>
         </is>
       </c>
     </row>
@@ -33942,6 +36136,18 @@
       <c r="G27" t="n">
         <v>37.42</v>
       </c>
+      <c r="H27" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="I27" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="J27" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="K27" t="n">
+        <v>86.42</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -34469,6 +36675,18 @@
       <c r="G44" t="n">
         <v>14.8</v>
       </c>
+      <c r="H44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K44" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -35988,6 +38206,18 @@
       <c r="G93" t="n">
         <v>5.22</v>
       </c>
+      <c r="H93" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J93" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="K93" t="n">
+        <v>5.28</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -36329,6 +38559,18 @@
       <c r="G104" t="n">
         <v>62.88</v>
       </c>
+      <c r="H104" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="I104" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="J104" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="K104" t="n">
+        <v>62.88</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -36484,6 +38726,18 @@
       <c r="G109" t="n">
         <v>41.54</v>
       </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>41.54</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -36515,6 +38769,18 @@
       <c r="G110" t="n">
         <v>34.84</v>
       </c>
+      <c r="H110" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="I110" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="J110" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="K110" t="n">
+        <v>34.84</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -36577,6 +38843,18 @@
       <c r="G112" t="n">
         <v>43.32</v>
       </c>
+      <c r="H112" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="I112" t="n">
+        <v>14.4133</v>
+      </c>
+      <c r="J112" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="K112" t="n">
+        <v>57.65</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -36794,6 +39072,18 @@
       <c r="G119" t="n">
         <v>17.598</v>
       </c>
+      <c r="H119" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="I119" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J119" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K119" t="n">
+        <v>32.9</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -36979,6 +39269,18 @@
       </c>
       <c r="G125" t="n">
         <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>17.9067</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>53.72</v>
       </c>
     </row>
     <row r="126">
